--- a/data/employees/EMP037/AST-EMP037-06.xlsx
+++ b/data/employees/EMP037/AST-EMP037-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vendor Comparison" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,166 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Vendor Comparison - Riley Patel (Procurement)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Riley Patel | Role: Senior Engineer | Location: Fremont | Date: 2025-02-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp037 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>70</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp037 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>85</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Vendor</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>On-Time %</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Quality %</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Spend YTD ($K)</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp037 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>97</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Acme Components</t>
+          <t>EMP037</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D5" t="n">
-        <v>97</v>
+          <t>Ast Emp037 06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-W04</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>99</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1450</v>
+        <v>84</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GlobalParts Inc</t>
+          <t>EMP037</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mechanical</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D6" t="n">
-        <v>91</v>
+          <t>Ast Emp037 06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-W05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>96</v>
-      </c>
-      <c r="F6" t="n">
-        <v>820</v>
+        <v>81</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TechSupply Co</t>
+          <t>EMP037</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>99</v>
+          <t>Ast Emp037 06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>98</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2100</v>
+        <v>67</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CleanRoom Solutions</t>
+          <t>EMP037</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Consumables</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D8" t="n">
+          <t>Ast Emp037 06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>78</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp037 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>66</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp037 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>76</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp037 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>76</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp037 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
         <v>88</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp037 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>60</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp037 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>72</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp037 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>65</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp037 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>98</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp037 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>88</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp037 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>85</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp037 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>65</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp037 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>73</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp037 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>94</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp037 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
         <v>95</v>
       </c>
-      <c r="F8" t="n">
-        <v>340</v>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp037 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>68</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp037 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>69</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp037 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>87</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP037</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP037 contributes to ast emp037 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>